--- a/raw-data/excel fire histories.xlsx
+++ b/raw-data/excel fire histories.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TSF_effect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A371FB43-71A1-4EA2-A21B-36E8E75A52DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27280139-9C35-4E7E-B091-AA8106742E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
   </bookViews>
   <sheets>
     <sheet name="manager" sheetId="1" r:id="rId1"/>
@@ -214,9 +214,6 @@
     <t>for landsat, all dates are the average of the last non-burned pictures' date and the first burned pictures' date</t>
   </si>
   <si>
-    <t>FILE NOT FINALIZED</t>
-  </si>
-  <si>
     <t>FILE CURRENT AS OF 2/24/25</t>
   </si>
   <si>
@@ -245,6 +242,10 @@
   </si>
   <si>
     <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire_4_30_2025_B1.pdf</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>FILE CURRENT AS OF 8/27/25</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -730,7 +731,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="34.9" x14ac:dyDescent="0.9">
       <c r="A1" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
@@ -853,13 +854,13 @@
         <v>45777</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -943,7 +944,7 @@
         <v>33664</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -961,7 +962,7 @@
         <v>34363</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -979,7 +980,7 @@
         <v>34747</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
@@ -997,7 +998,7 @@
         <v>35087</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
@@ -1015,7 +1016,7 @@
         <v>35525</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1033,7 +1034,7 @@
         <v>36242</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -1051,7 +1052,7 @@
         <v>36917</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -1069,7 +1070,7 @@
         <v>37690</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
@@ -1087,7 +1088,7 @@
         <v>38389</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
@@ -1105,7 +1106,7 @@
         <v>40567</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
@@ -1123,7 +1124,7 @@
         <v>40942</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
@@ -1141,7 +1142,7 @@
         <v>41315</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
@@ -1159,7 +1160,7 @@
         <v>42202</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
@@ -1177,7 +1178,7 @@
         <v>42817</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
@@ -1195,7 +1196,7 @@
         <v>44235</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1213,7 +1214,7 @@
         <v>45068</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
@@ -1567,7 +1568,7 @@
         <v>32904</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
@@ -1585,7 +1586,7 @@
         <v>34001</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
@@ -1603,7 +1604,7 @@
         <v>34747</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
@@ -1621,7 +1622,7 @@
         <v>35845</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
@@ -1639,7 +1640,7 @@
         <v>37663</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
@@ -1657,7 +1658,7 @@
         <v>39083</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
@@ -1675,7 +1676,7 @@
         <v>40205</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
@@ -1693,7 +1694,7 @@
         <v>41294</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
@@ -1711,7 +1712,7 @@
         <v>42024</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
@@ -1729,7 +1730,7 @@
         <v>42962</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
@@ -1747,7 +1748,7 @@
         <v>43696</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
@@ -1765,7 +1766,7 @@
         <v>44970</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
@@ -1856,7 +1857,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="34.9" x14ac:dyDescent="0.9">
       <c r="A1" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -1979,7 +1980,7 @@
         <v>45068</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
@@ -2114,7 +2115,7 @@
         <v>43696</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
@@ -2295,7 +2296,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="34.9" x14ac:dyDescent="0.9">
       <c r="A1" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
@@ -2949,7 +2950,7 @@
         <v>34777</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
         <v>52</v>
@@ -2969,7 +2970,7 @@
         <v>31433</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
         <v>52</v>
@@ -2989,7 +2990,7 @@
         <v>31929</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
         <v>52</v>

--- a/raw-data/excel fire histories.xlsx
+++ b/raw-data/excel fire histories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27280139-9C35-4E7E-B091-AA8106742E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EB20AB-1822-41C0-BCE0-9D505044281B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
   </bookViews>

--- a/raw-data/excel fire histories.xlsx
+++ b/raw-data/excel fire histories.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EB20AB-1822-41C0-BCE0-9D505044281B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C613EAD-1901-47B6-AA3F-D991C3CABB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
+    <workbookView xWindow="45960" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
   </bookViews>
   <sheets>
     <sheet name="manager" sheetId="1" r:id="rId1"/>
     <sheet name="field_notes" sheetId="2" r:id="rId2"/>
     <sheet name="landsat" sheetId="3" r:id="rId3"/>
+    <sheet name="landscape" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">field_notes!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">manager!$A$2:$E$60</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="69">
+  <si>
+    <t>FILE CURRENT AS OF 2/24/25</t>
+  </si>
   <si>
     <t>fire_date</t>
   </si>
@@ -54,133 +58,158 @@
     <t>path</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>date_uncertain</t>
+  </si>
+  <si>
+    <t>fire_uncertain</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
     <t>manager</t>
   </si>
   <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2008_2.pdf</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;BraggShapefiles_WadeWall_USGS.pdf</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2015-2019.pdf</t>
+  </si>
+  <si>
+    <t>Controlled burn at B1 for our burn experiments occurred on 2018-06-08, but did not reach census plts</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2022.pdf</t>
+  </si>
+  <si>
+    <t>B1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire_4_30_2025_B1.pdf</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>GSP-BI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>VFT&gt;VFT fire history data&gt;Email records&gt;GSP_NathanBurmester_fires2017-203 fires.csv</t>
   </si>
   <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2005-2019.pdf</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>uncertain whether fire happened-- CM in a firebreak</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Croatan_Allison_Heather_ Fwd_CM burning in 2016.pdf</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2020.pdf</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2022.pdf</t>
+  </si>
+  <si>
     <t>IA</t>
   </si>
   <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CampLejeune_GaryHaught_2005-2020.pdf</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CampLejeune_GaryHaught_April2023_update.pdf</t>
+  </si>
+  <si>
+    <t>GSP-LI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>ME</t>
   </si>
   <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>CM</t>
-  </si>
-  <si>
     <t>used this link: https://gec.cr.usgs.gov/outgoing/baecv/LBA/LBA_CU_C01_V01/</t>
   </si>
   <si>
-    <t>CH</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2008_2.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CampLejeune_GaryHaught_2005-2020.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2015-2019.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2005-2019.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;BraggShapefiles_WadeWall_USGS.pdf</t>
-  </si>
-  <si>
-    <t>uncertain whether fire happened-- CM in a firebreak</t>
-  </si>
-  <si>
     <t>field_notes</t>
   </si>
   <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2015-2019.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>date from manager</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2022.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>date from manager; Controlled burn at B1 for our burn experiments occurred on 2018-06-08, but did not reach census plts</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;GSP_NathanBurmester_fires2017-203 fires.csv, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Croatan_Allison_Heather_ Fwd_CM burning in 2016.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2005-2019.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2020.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2022.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CampLejeune_GaryHaught_April2023_update.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+  </si>
+  <si>
+    <t>date from: https://gec.cr.usgs.gov/outgoing/baecv/LBA/LBA_CU_C01_V01/</t>
+  </si>
+  <si>
     <t>VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
   </si>
   <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2015-2019.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2022.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;GSP_NathanBurmester_fires2017-203 fires.csv, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Croatan_Allison_Heather_ Fwd_CM burning in 2016.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2005-2019.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2020.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2022.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CampLejeune_GaryHaught_April2023_update.pdf, VFT&gt;VFT fire history data&gt;FireObservations_ExtractedFromFieldNotes.docx</t>
+    <t xml:space="preserve"> fire in 2018-03-01 did not reach our plots</t>
   </si>
   <si>
     <t>fire in 2018-03-01 did not reach our plots</t>
-  </si>
-  <si>
-    <t>Controlled burn at B1 for our burn experiments occurred on 2018-06-08, but did not reach census plts</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire2022.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Croatan_Allison_Heather_ Fwd_CM burning in 2016.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2020.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CroatanNF_AndyWalker_Fire2022.pdf</t>
-  </si>
-  <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;CampLejeune_GaryHaught_April2023_update.pdf</t>
-  </si>
-  <si>
-    <t>date_uncertain</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>fire_uncertain</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fire in 2018-03-01 did not reach our plots</t>
-  </si>
-  <si>
-    <t>date from manager</t>
-  </si>
-  <si>
-    <t>date from manager; Controlled burn at B1 for our burn experiments occurred on 2018-06-08, but did not reach census plts</t>
-  </si>
-  <si>
-    <t>date from: https://gec.cr.usgs.gov/outgoing/baecv/LBA/LBA_CU_C01_V01/</t>
   </si>
   <si>
     <t>GSP-BI</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
+    <t>Landsat</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>for landsat, all dates are the average of the last non-burned pictures' date and the first burned pictures' date</t>
+  </si>
+  <si>
     <t>GSP-LI</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -205,47 +234,39 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>Landsat</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>for landsat, all dates are the average of the last non-burned pictures' date and the first burned pictures' date</t>
-  </si>
-  <si>
-    <t>FILE CURRENT AS OF 2/24/25</t>
-  </si>
-  <si>
     <t>B2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>B1</t>
+    <t>FILE CURRENT AS OF 11/14/25</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>GSP-BI</t>
+    <t>FILE CURRENT AS OF 11/14/25</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>GSP-LI</t>
+    <t xml:space="preserve"> landscape fire records were produced based on the manager records. Occurrences of fires were confirmed using Landsat false color images (SWIR, NIR, Blue).</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>GSP-BI</t>
+    <t>startyear</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>GSP-LI</t>
+    <t>CH</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>VFT&gt;VFT fire history data&gt;Email records&gt;Bragg_StacyHuskins_Fire_4_30_2025_B1.pdf</t>
+    <t>CM</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>FILE CURRENT AS OF 8/27/25</t>
+    <t>IA</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ME</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -723,38 +744,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B609A7-77BB-AE4A-B6B2-C4ACEA0133DD}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.87890625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="4" max="4" width="28.46875" customWidth="1"/>
+    <col min="4" max="4" width="82.87890625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="34.9" x14ac:dyDescent="0.9">
       <c r="A1" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -762,17 +783,17 @@
         <v>39508</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -780,17 +801,17 @@
         <v>41343</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -798,19 +819,19 @@
         <v>42529</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -818,17 +839,17 @@
         <v>43540</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -836,17 +857,17 @@
         <v>44707</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -854,13 +875,13 @@
         <v>45777</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -870,17 +891,17 @@
         <v>39600</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -888,19 +909,19 @@
         <v>42532</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -908,17 +929,17 @@
         <v>43540</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -926,17 +947,17 @@
         <v>44707</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
@@ -944,17 +965,17 @@
         <v>33664</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -962,17 +983,17 @@
         <v>34363</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -980,17 +1001,17 @@
         <v>34747</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -998,17 +1019,17 @@
         <v>35087</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -1016,17 +1037,17 @@
         <v>35525</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -1034,17 +1055,17 @@
         <v>36242</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
@@ -1052,17 +1073,17 @@
         <v>36917</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -1070,17 +1091,17 @@
         <v>37690</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
@@ -1088,17 +1109,17 @@
         <v>38389</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
@@ -1106,17 +1127,17 @@
         <v>40567</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
@@ -1124,17 +1145,17 @@
         <v>40942</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
@@ -1142,17 +1163,17 @@
         <v>41315</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
@@ -1160,17 +1181,17 @@
         <v>42202</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
@@ -1178,17 +1199,17 @@
         <v>42817</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
@@ -1196,17 +1217,17 @@
         <v>44235</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
@@ -1214,17 +1235,17 @@
         <v>45068</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
@@ -1232,17 +1253,17 @@
         <v>38381</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
@@ -1250,17 +1271,17 @@
         <v>39027</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -1268,17 +1289,17 @@
         <v>40134</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -1286,22 +1307,22 @@
         <v>38737</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
@@ -1309,22 +1330,22 @@
         <v>39094</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
@@ -1332,22 +1353,22 @@
         <v>39850</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
@@ -1355,17 +1376,17 @@
         <v>40015</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
@@ -1373,45 +1394,43 @@
         <v>40978</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>38</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="7">
         <v>40980</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
@@ -1419,17 +1438,17 @@
         <v>42430</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
@@ -1437,22 +1456,22 @@
         <v>42915</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
@@ -1460,17 +1479,17 @@
         <v>43156</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
@@ -1478,17 +1497,17 @@
         <v>43892</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
@@ -1496,17 +1515,17 @@
         <v>44624</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
@@ -1514,17 +1533,17 @@
         <v>40939</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
@@ -1532,17 +1551,17 @@
         <v>42048</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
@@ -1550,17 +1569,17 @@
         <v>43871</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
@@ -1568,17 +1587,17 @@
         <v>32904</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
@@ -1586,17 +1605,17 @@
         <v>34001</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
@@ -1604,17 +1623,17 @@
         <v>34747</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
@@ -1622,17 +1641,17 @@
         <v>35845</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
@@ -1640,17 +1659,17 @@
         <v>37663</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
@@ -1658,17 +1677,17 @@
         <v>39083</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
@@ -1676,17 +1695,17 @@
         <v>40205</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
@@ -1694,17 +1713,17 @@
         <v>41294</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.4">
@@ -1712,17 +1731,17 @@
         <v>42024</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.4">
@@ -1730,17 +1749,17 @@
         <v>42962</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.4">
@@ -1748,17 +1767,17 @@
         <v>43696</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.4">
@@ -1766,17 +1785,17 @@
         <v>44970</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
@@ -1784,17 +1803,17 @@
         <v>40939</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.4">
@@ -1802,17 +1821,17 @@
         <v>42048</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.4">
@@ -1820,19 +1839,19 @@
         <v>43900</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.4">
@@ -1853,34 +1872,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C5F246-917A-DB45-9A6A-503E61453CAC}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.87890625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="34.9" x14ac:dyDescent="0.9">
       <c r="A1" s="4" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -1888,22 +1907,22 @@
         <v>43540</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -1911,22 +1930,22 @@
         <v>44707</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -1934,22 +1953,22 @@
         <v>42532</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -1957,22 +1976,22 @@
         <v>44707</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -1980,22 +1999,22 @@
         <v>45068</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2003,19 +2022,19 @@
         <v>42430</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2023,22 +2042,22 @@
         <v>43156</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2046,22 +2065,22 @@
         <v>43892</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2069,22 +2088,22 @@
         <v>44624</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2092,22 +2111,22 @@
         <v>43871</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2115,22 +2134,22 @@
         <v>43696</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2138,22 +2157,22 @@
         <v>43900</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2161,19 +2180,19 @@
         <v>44256</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2181,22 +2200,22 @@
         <v>42795</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2204,19 +2223,19 @@
         <v>44256</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2224,22 +2243,22 @@
         <v>42795</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2247,19 +2266,19 @@
         <v>44986</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -2267,19 +2286,19 @@
         <v>42795</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2291,35 +2310,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D715BE-6D22-334F-97CD-3B59221D3F48}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultColWidth="10.87890625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="34.9" x14ac:dyDescent="0.9">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -2327,682 +2346,1025 @@
         <v>38443</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
-        <v>39265</v>
+        <v>40593</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
         <v>52</v>
       </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
-        <v>40593</v>
+        <v>41363</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
         <v>52</v>
       </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
-        <v>41363</v>
+        <v>42818</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
-        <v>42818</v>
+        <v>39123</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
-        <v>39123</v>
+        <v>40213</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
-        <v>40213</v>
+        <v>41363</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
-        <v>41363</v>
+        <v>42017</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
         <v>52</v>
       </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
-        <v>42017</v>
+        <v>43690</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
-        <v>43690</v>
+        <v>44993</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
-        <v>44993</v>
+        <v>38768</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
-        <v>38768</v>
+        <v>39857</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
-        <v>39857</v>
+        <v>42046</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
-        <v>42046</v>
+        <v>43870</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
-        <v>43870</v>
+        <v>45054</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
-        <v>45054</v>
+        <v>36842</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
-        <v>36842</v>
+        <v>38388</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
         <v>52</v>
       </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
-        <v>38388</v>
+        <v>44286</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
         <v>52</v>
       </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
-        <v>44286</v>
+        <v>35359</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
         <v>52</v>
       </c>
-      <c r="D21" t="s">
-        <v>53</v>
-      </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
-        <v>35359</v>
+        <v>36554</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
         <v>52</v>
       </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
-        <v>36554</v>
+        <v>42462</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
         <v>52</v>
       </c>
-      <c r="D23" t="s">
-        <v>53</v>
-      </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
-        <v>42462</v>
+        <v>43902</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
         <v>52</v>
       </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
-        <v>43902</v>
+        <v>44654</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
         <v>52</v>
       </c>
-      <c r="D25" t="s">
-        <v>53</v>
-      </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
-        <v>44654</v>
+        <v>38362</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
         <v>52</v>
       </c>
-      <c r="D26" t="s">
-        <v>53</v>
-      </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
-        <v>38362</v>
+        <v>39971</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
         <v>52</v>
       </c>
-      <c r="D27" t="s">
-        <v>53</v>
-      </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
-        <v>39983</v>
+        <v>42783</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
         <v>52</v>
       </c>
-      <c r="D28" t="s">
-        <v>53</v>
-      </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
-        <v>40334</v>
+        <v>43902</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
         <v>52</v>
       </c>
-      <c r="D29" t="s">
-        <v>53</v>
-      </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
-        <v>42783</v>
+        <v>39560</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" t="s">
         <v>52</v>
       </c>
-      <c r="D30" t="s">
-        <v>53</v>
-      </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
-        <v>43902</v>
+        <v>34777</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
         <v>52</v>
       </c>
-      <c r="D31" t="s">
-        <v>53</v>
-      </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
-        <v>44735</v>
+        <v>31433</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
         <v>52</v>
       </c>
-      <c r="D32" t="s">
-        <v>53</v>
-      </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
-        <v>39560</v>
+        <v>31929</v>
       </c>
       <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
         <v>51</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>52</v>
       </c>
-      <c r="D33" t="s">
-        <v>53</v>
-      </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="1">
-        <v>34777</v>
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1E58FE-7144-4B59-9820-C76451FCA0F7}">
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="34.9" x14ac:dyDescent="0.9">
+      <c r="A1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>2007</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2012</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>2015</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>2018</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>2021</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>1994</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>2007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>2015</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>2018</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>2004</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>2015</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>2016</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>2020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>2022</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>2002</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>2006</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>2009</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>2012</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>2014</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>2017</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>2019</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>2022</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>2004</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>2006</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>2009</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>2020</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>2005</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" t="s">
-        <v>38</v>
-      </c>
-      <c r="G34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="1">
-        <v>31433</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>2008</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="1">
-        <v>31929</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>2011</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" t="s">
-        <v>38</v>
-      </c>
-      <c r="G36" t="s">
-        <v>39</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>2015</v>
+      </c>
+      <c r="B37" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>2017</v>
+      </c>
+      <c r="B38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>2019</v>
+      </c>
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>2021</v>
+      </c>
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>2011</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>2014</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>2019</v>
+      </c>
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>2022</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>2004</v>
+      </c>
+      <c r="B45" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>2008</v>
+      </c>
+      <c r="B46" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>2016</v>
+      </c>
+      <c r="B47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>2019</v>
+      </c>
+      <c r="B48" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/raw-data/excel fire histories.xlsx
+++ b/raw-data/excel fire histories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C613EAD-1901-47B6-AA3F-D991C3CABB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390E4BC5-11BC-4AEC-9D11-DD2D15966486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45960" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="3" xr2:uid="{58B67793-E89C-414F-A104-ABAD252BA177}"/>
   </bookViews>
   <sheets>
     <sheet name="manager" sheetId="1" r:id="rId1"/>
